--- a/data/trans_camb/P1423-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,73</t>
+          <t>-0,02; 1,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,51</t>
+          <t>-0,01; 2,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,6</t>
+          <t>0,53; 6,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,77</t>
+          <t>-2,86; 0,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,87</t>
+          <t>-1,64; 2,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 8,76</t>
+          <t>0,23; 8,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,87</t>
+          <t>-1,22; 0,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,92</t>
+          <t>-0,42; 2,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,48</t>
+          <t>0,64; 5,11</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,19; 61,99</t>
+          <t>-83,13; 60,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,32; 179,03</t>
+          <t>-49,47; 195,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 526,37</t>
+          <t>-4,46; 531,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 99,15</t>
+          <t>-67,85; 123,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 204,42</t>
+          <t>-30,3; 234,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,51; 609,49</t>
+          <t>25,81; 532,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,82</t>
+          <t>-0,42; 2,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,41</t>
+          <t>-1,97; 0,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,89</t>
+          <t>-1,22; 3,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,17</t>
+          <t>-1,51; 3,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,76</t>
+          <t>-3,14; 0,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,82</t>
+          <t>-0,35; 5,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,47</t>
+          <t>-0,27; 2,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,25</t>
+          <t>-2,08; 0,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,01</t>
+          <t>0,3; 4,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 224,31</t>
+          <t>-21,62; 235,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-79,16; 44,14</t>
+          <t>-76,29; 53,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 226,43</t>
+          <t>-53,08; 235,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 118,91</t>
+          <t>-31,45; 134,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,02; 32,98</t>
+          <t>-66,88; 30,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 213,73</t>
+          <t>-6,5; 228,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 120,94</t>
+          <t>-11,48; 119,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,86; 16,19</t>
+          <t>-62,41; 11,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 187,82</t>
+          <t>7,03; 190,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,08</t>
+          <t>-1,41; 2,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,27</t>
+          <t>-2,28; 1,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,72</t>
+          <t>0,44; 5,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,67</t>
+          <t>0,92; 6,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,41</t>
+          <t>-1,77; 3,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,08</t>
+          <t>-1,73; 3,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,31</t>
+          <t>0,7; 4,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,56</t>
+          <t>-1,43; 1,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,91</t>
+          <t>0,49; 4,02</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 152,94</t>
+          <t>-35,18; 132,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-59,78; 66,66</t>
+          <t>-58,96; 77,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,71; 277,13</t>
+          <t>5,38; 255,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 142,39</t>
+          <t>12,86; 157,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 73,94</t>
+          <t>-25,5; 73,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 86,96</t>
+          <t>-23,82; 85,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,53; 117,56</t>
+          <t>12,62; 125,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 44,64</t>
+          <t>-26,91; 46,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 105,38</t>
+          <t>9,17; 113,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,73</t>
+          <t>-0,75; 4,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,08</t>
+          <t>-1,21; 3,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,5</t>
+          <t>-1,13; 5,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,96</t>
+          <t>-2,73; 5,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 4,17</t>
+          <t>-3,27; 4,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,62</t>
+          <t>-2,62; 4,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,54</t>
+          <t>-0,74; 3,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,27</t>
+          <t>-1,27; 3,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,0</t>
+          <t>-2,22; 4,25</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 198,52</t>
+          <t>-21,21; 208,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 164,81</t>
+          <t>-31,4; 169,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 229,86</t>
+          <t>-27,81; 247,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 53,04</t>
+          <t>-20,67; 58,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 44,23</t>
+          <t>-24,65; 53,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 50,01</t>
+          <t>-18,96; 51,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 58,78</t>
+          <t>-8,88; 65,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 57,51</t>
+          <t>-15,4; 54,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 63,3</t>
+          <t>-26,32; 65,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 4,99</t>
+          <t>-1,76; 5,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,17</t>
+          <t>-2,08; 4,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,3</t>
+          <t>0,6; 6,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 10,41</t>
+          <t>0,56; 11,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,97</t>
+          <t>0,14; 9,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 8,5</t>
+          <t>0,65; 8,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,48</t>
+          <t>0,63; 6,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,02</t>
+          <t>-0,1; 5,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,62</t>
+          <t>1,52; 6,69</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 119,76</t>
+          <t>-26,98; 121,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 100,47</t>
+          <t>-31,39; 114,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,34; 182,65</t>
+          <t>6,62; 172,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,97; 96,99</t>
+          <t>3,56; 110,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,93; 98,96</t>
+          <t>-0,51; 98,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 82,31</t>
+          <t>3,95; 88,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,3; 81,45</t>
+          <t>4,51; 80,07</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 75,0</t>
+          <t>-0,79; 70,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13,44; 85,49</t>
+          <t>14,07; 85,97</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,18</t>
+          <t>-3,49; 3,84</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,43</t>
+          <t>-5,49; 0,53</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,06</t>
+          <t>-3,8; 2,24</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,15</t>
+          <t>2,84; 13,54</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,37; 10,22</t>
+          <t>0,29; 11,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 5,15</t>
+          <t>-8,99; 5,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,64; 7,15</t>
+          <t>0,52; 7,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,25</t>
+          <t>-1,54; 4,98</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 2,82</t>
+          <t>-5,71; 2,82</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-51,71; 116,47</t>
+          <t>-51,14; 111,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 18,29</t>
+          <t>-76,18; 21,91</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-55,45; 54,21</t>
+          <t>-51,59; 64,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18,23; 143,55</t>
+          <t>19,16; 143,53</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,69; 109,8</t>
+          <t>2,46; 123,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 47,75</t>
+          <t>-62,7; 50,23</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,91; 96,97</t>
+          <t>5,08; 102,02</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 70,8</t>
+          <t>-15,19; 66,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 34,68</t>
+          <t>-54,02; 35,64</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,62</t>
+          <t>-4,92; 5,42</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,14</t>
+          <t>-5,87; 3,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 6,16</t>
+          <t>-2,96; 6,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,57; 14,76</t>
+          <t>3,71; 14,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 11,05</t>
+          <t>-0,19; 10,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,37</t>
+          <t>1,77; 10,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,52; 9,32</t>
+          <t>1,39; 9,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 6,33</t>
+          <t>-0,68; 6,6</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,08</t>
+          <t>1,03; 7,49</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-57,25; 98,43</t>
+          <t>-54,18; 113,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-57,7; 77,44</t>
+          <t>-56,0; 75,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 141,56</t>
+          <t>-31,37; 135,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26,29; 206,74</t>
+          <t>28,51; 194,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,7; 147,7</t>
+          <t>-1,85; 139,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,76; 147,82</t>
+          <t>12,37; 146,23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,75; 133,49</t>
+          <t>10,55; 137,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 87,93</t>
+          <t>-6,48; 96,09</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>13,68; 123,61</t>
+          <t>8,6; 111,95</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,07</t>
+          <t>0,09; 1,98</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,96</t>
+          <t>-0,68; 0,94</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,7</t>
+          <t>1,29; 3,7</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,09</t>
+          <t>2,34; 5,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,95</t>
+          <t>1,13; 4,07</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,04</t>
+          <t>1,16; 4,9</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,34</t>
+          <t>1,62; 3,31</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,17</t>
+          <t>0,68; 2,28</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,09</t>
+          <t>1,88; 4,14</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5,29; 74,33</t>
+          <t>1,93; 73,93</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 36,47</t>
+          <t>-18,91; 34,96</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>39,35; 137,32</t>
+          <t>38,28; 132,47</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>27,61; 73,02</t>
+          <t>28,59; 76,61</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>13,9; 56,6</t>
+          <t>13,83; 60,88</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,09; 69,94</t>
+          <t>16,31; 69,48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,76; 65,9</t>
+          <t>27,85; 64,98</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9,31; 44,22</t>
+          <t>11,55; 45,31</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>33,4; 81,69</t>
+          <t>33,54; 82,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1423-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>3,03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,62</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,67</t>
+          <t>-0,1; 1,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,15</t>
+          <t>0,03; 2,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,69</t>
+          <t>0,63; 5,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,86</t>
+          <t>-2,85; 0,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,94</t>
+          <t>-1,59; 2,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 8,92</t>
+          <t>-0,04; 7,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,93</t>
+          <t>-1,16; 0,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,06</t>
+          <t>-0,48; 2,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,11</t>
+          <t>0,71; 4,89</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1057,58%</t>
+          <t>1212,16%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>147,28%</t>
+          <t>119,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>200,89%</t>
+          <t>197,65%</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 60,38</t>
+          <t>-83,29; 71,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 195,03</t>
+          <t>-48,69; 191,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 531,2</t>
+          <t>-7,15; 427,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,85; 123,66</t>
+          <t>-63,79; 114,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 234,55</t>
+          <t>-30,27; 238,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,81; 532,18</t>
+          <t>31,89; 530,81</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>3,61</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,92</t>
+          <t>-0,53; 2,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,58</t>
+          <t>-2,05; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,12</t>
+          <t>-0,49; 3,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,33</t>
+          <t>-1,38; 3,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,72</t>
+          <t>-3,02; 0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,91</t>
+          <t>1,08; 6,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,54</t>
+          <t>-0,36; 2,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,21</t>
+          <t>-1,92; 0,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,08</t>
+          <t>0,69; 4,29</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>102,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,62; 235,94</t>
+          <t>-24,98; 216,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,29; 53,82</t>
+          <t>-79,86; 52,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,08; 235,12</t>
+          <t>-27,95; 283,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 134,01</t>
+          <t>-31,04; 125,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,88; 30,01</t>
+          <t>-66,85; 34,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 228,65</t>
+          <t>17,85; 273,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 119,69</t>
+          <t>-15,08; 109,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 11,56</t>
+          <t>-59,71; 17,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 190,51</t>
+          <t>23,11; 205,43</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,44</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,94</t>
+          <t>-1,32; 3,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,38</t>
+          <t>-2,36; 1,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,34</t>
+          <t>0,36; 5,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,89</t>
+          <t>1,05; 6,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,44</t>
+          <t>-1,57; 3,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,97</t>
+          <t>-0,6; 4,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,53</t>
+          <t>0,63; 4,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,69</t>
+          <t>-1,37; 1,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,02</t>
+          <t>0,39; 3,95</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 132,39</t>
+          <t>-36,75; 145,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,96; 77,26</t>
+          <t>-59,41; 70,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,38; 255,11</t>
+          <t>2,14; 230,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,86; 157,32</t>
+          <t>13,21; 153,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 73,61</t>
+          <t>-21,56; 76,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 85,63</t>
+          <t>-8,73; 103,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 125,74</t>
+          <t>10,08; 121,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 46,91</t>
+          <t>-26,43; 54,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 113,46</t>
+          <t>6,46; 105,29</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>3,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,13</t>
+          <t>-0,59; 4,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,31</t>
+          <t>-1,2; 3,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,74</t>
+          <t>2,14; 7,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,58</t>
+          <t>-2,47; 5,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 4,66</t>
+          <t>-3,64; 4,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,74</t>
+          <t>-1,27; 5,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,79</t>
+          <t>-0,62; 3,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,16</t>
+          <t>-1,41; 3,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,25</t>
+          <t>1,41; 5,71</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>158,55%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 208,63</t>
+          <t>-16,66; 220,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 169,35</t>
+          <t>-32,39; 181,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 247,7</t>
+          <t>45,02; 385,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 58,46</t>
+          <t>-18,81; 60,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 53,45</t>
+          <t>-27,81; 45,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 51,97</t>
+          <t>-9,61; 63,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 65,51</t>
+          <t>-7,71; 61,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 54,28</t>
+          <t>-16,99; 49,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 65,83</t>
+          <t>15,74; 95,8</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>4,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,14</t>
+          <t>-1,6; 5,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,63</t>
+          <t>-2,39; 4,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,91</t>
+          <t>0,28; 6,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 11,0</t>
+          <t>0,75; 10,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 9,92</t>
+          <t>-0,27; 9,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 8,86</t>
+          <t>0,27; 8,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,62</t>
+          <t>0,77; 6,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,64</t>
+          <t>-0,09; 6,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,69</t>
+          <t>1,47; 6,46</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,98; 121,26</t>
+          <t>-24,0; 127,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 114,17</t>
+          <t>-35,02; 104,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,62; 172,55</t>
+          <t>4,9; 176,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,56; 110,1</t>
+          <t>4,05; 95,92</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 98,69</t>
+          <t>-1,71; 96,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,95; 88,41</t>
+          <t>1,69; 86,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,51; 80,07</t>
+          <t>7,31; 85,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 70,15</t>
+          <t>-0,94; 77,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14,07; 85,97</t>
+          <t>13,02; 84,11</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,71</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,5</t>
+          <t>3,94</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>1,57</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,84</t>
+          <t>-3,86; 3,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,53</t>
+          <t>-5,66; 0,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,24</t>
+          <t>-3,97; 2,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,84; 13,54</t>
+          <t>2,29; 12,9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,29; 11,12</t>
+          <t>0,15; 10,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 5,49</t>
+          <t>-0,31; 7,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,52; 7,46</t>
+          <t>0,41; 7,27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,98</t>
+          <t>-1,12; 5,02</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 2,82</t>
+          <t>-1,15; 4,37</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-9,06%</t>
+          <t>-13,55%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-12,69%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-6,38%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 111,16</t>
+          <t>-56,5; 105,18</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,18; 21,91</t>
+          <t>-77,39; 22,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-51,59; 64,43</t>
+          <t>-55,06; 61,76</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19,16; 143,53</t>
+          <t>16,53; 139,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,46; 123,63</t>
+          <t>0,45; 113,33</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-62,7; 50,23</t>
+          <t>-3,08; 75,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,08; 102,02</t>
+          <t>3,6; 98,01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 66,75</t>
+          <t>-11,65; 70,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-54,02; 35,64</t>
+          <t>-11,91; 62,85</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,43</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>4,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 5,42</t>
+          <t>-5,17; 4,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 3,27</t>
+          <t>-5,89; 2,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 6,14</t>
+          <t>-2,66; 5,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,71; 14,28</t>
+          <t>3,64; 14,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 10,46</t>
+          <t>0,35; 10,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,44</t>
+          <t>2,13; 10,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,39; 9,36</t>
+          <t>1,77; 9,17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 6,6</t>
+          <t>-0,65; 6,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,49</t>
+          <t>1,23; 8,22</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 113,54</t>
+          <t>-56,84; 121,87</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-56,0; 75,79</t>
+          <t>-60,06; 64,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 135,39</t>
+          <t>-29,06; 134,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>28,51; 194,01</t>
+          <t>27,35; 187,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 139,46</t>
+          <t>1,23; 144,41</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,37; 146,23</t>
+          <t>15,25; 157,23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,55; 137,06</t>
+          <t>15,86; 127,93</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 96,09</t>
+          <t>-7,12; 90,28</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8,6; 111,95</t>
+          <t>11,22; 126,3</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,85</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,98</t>
+          <t>0,1; 2,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,94</t>
+          <t>-0,74; 1,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,7</t>
+          <t>1,95; 4,04</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,24</t>
+          <t>2,49; 5,19</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,07</t>
+          <t>1,12; 3,99</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,9</t>
+          <t>3,37; 6,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,31</t>
+          <t>1,65; 3,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,28</t>
+          <t>0,54; 2,23</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,14</t>
+          <t>2,99; 4,66</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1,93; 73,93</t>
+          <t>0,43; 74,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 34,96</t>
+          <t>-21,42; 38,12</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>38,28; 132,47</t>
+          <t>54,72; 152,84</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>28,59; 76,61</t>
+          <t>30,21; 74,69</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>13,83; 60,88</t>
+          <t>13,69; 57,96</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,31; 69,48</t>
+          <t>40,07; 86,59</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,85; 64,98</t>
+          <t>28,41; 67,65</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>11,55; 45,31</t>
+          <t>9,0; 45,16</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>33,54; 82,09</t>
+          <t>51,88; 95,39</t>
         </is>
       </c>
     </row>
